--- a/SchandomOutput.xlsx
+++ b/SchandomOutput.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Horde Chess</t>
+          <t>Go Moku</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pinguin</t>
+          <t>Pente</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -978,7 +978,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Horde Chess</t>
+          <t>Go Moku</t>
         </is>
       </c>
       <c r="G22" t="n">
